--- a/loss-time/outputs/Loss_time_S32_05-10_den_19-10.xlsx
+++ b/loss-time/outputs/Loss_time_S32_05-10_den_19-10.xlsx
@@ -7849,7 +7849,7 @@
     <row r="10">
       <c r="A10" s="52" t="inlineStr">
         <is>
-          <t>9. Veneer (làm mẫu): 10/10 (2 người 9:00-10:30, 3 giờ, bộ phận TF) và 15/10 (1 người 8:00-8:20, ME). Khu vực ghi RC - PANEL (giả định).</t>
+          <t>9. Veneer (làm mẫu): 10/10 (2 người 9:00-10:30, 3 giờ, bộ phận TF) và 15/10 (1 người 8:00-8:20, ME). Khu vực ghi RC - PANEL (Raw Cutting, người dùng xác nhận 20/10).</t>
         </is>
       </c>
     </row>
